--- a/Sufficient data WITH_PO/B0F3PQWDP8_fallback_WITH_PO.xlsx
+++ b/Sufficient data WITH_PO/B0F3PQWDP8_fallback_WITH_PO.xlsx
@@ -487,11 +487,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45816</v>
+        <v>45830</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -499,10 +499,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -525,11 +525,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W26</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45823</v>
+        <v>45837</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -563,11 +563,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W27</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45830</v>
+        <v>45844</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -601,11 +601,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W26</t>
+          <t>W28</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45837</v>
+        <v>45851</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -639,11 +639,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W27</t>
+          <t>W29</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45844</v>
+        <v>45858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -677,11 +677,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W28</t>
+          <t>W30</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45851</v>
+        <v>45865</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -715,11 +715,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W29</t>
+          <t>W31</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45858</v>
+        <v>45872</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -753,11 +753,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W30</t>
+          <t>W32</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45865</v>
+        <v>45879</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -791,11 +791,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W31</t>
+          <t>W33</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45872</v>
+        <v>45886</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -829,11 +829,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>W32</t>
+          <t>W34</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45879</v>
+        <v>45893</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -867,11 +867,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>W33</t>
+          <t>W35</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45886</v>
+        <v>45900</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -905,11 +905,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>W34</t>
+          <t>W36</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45893</v>
+        <v>45907</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -943,11 +943,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>W35</t>
+          <t>W37</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45900</v>
+        <v>45914</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -981,11 +981,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>W36</t>
+          <t>W38</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45907</v>
+        <v>45921</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1019,11 +1019,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>W37</t>
+          <t>W39</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45914</v>
+        <v>45928</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1057,11 +1057,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>W38</t>
+          <t>W40</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45921</v>
+        <v>45935</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
